--- a/docs/exports/division/Division_D.xlsx
+++ b/docs/exports/division/Division_D.xlsx
@@ -515,14 +515,14 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:24  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Division D — Level Totals (District Rank #1 of 9)</t>
+          <t>Division D — Level Totals (District Rank #2 of 9)</t>
         </is>
       </c>
     </row>
@@ -555,19 +555,19 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>89</v>
+        <v>19</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>244</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -608,7 +608,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:24  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -648,19 +648,19 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>4</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -711,7 +711,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:24  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -774,19 +774,19 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>115</v>
+        <v>25</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>5</v>
@@ -798,26 +798,26 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Area 04</t>
+          <t>Area 02</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -826,23 +826,23 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Area 02</t>
+          <t>Area 01</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>4</v>
@@ -854,26 +854,26 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Area 01</t>
+          <t>Area 04</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F10" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>32</v>
-      </c>
       <c r="H10" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -887,7 +887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -917,7 +917,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:24  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -985,19 +985,19 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G7" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H7" s="6" t="n">
         <v>20</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>84</v>
       </c>
     </row>
     <row r="8">
@@ -1006,28 +1006,28 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>IESL Toastmasters Club</t>
+          <t>Torrington Toastmasters Club</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G8" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="8" t="n">
         <v>6</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -1036,28 +1036,28 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Startup Colombo Toastmasters Club</t>
+          <t>CECB Toastmasters Club</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -1066,28 +1066,28 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Moratuwa Toastmasters</t>
+          <t>IESL Toastmasters Club</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="8" t="n">
         <v>3</v>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -1096,28 +1096,28 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>HSBC Global Service Centre</t>
+          <t>Sri Lanka Institute of Marketing Toastmasters Club</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="12">
@@ -1126,28 +1126,28 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>CECB Toastmasters Club</t>
+          <t>IESL Ruhuna Toastmasters Club</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="8" t="n">
         <v>2</v>
-      </c>
-      <c r="G12" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -1156,28 +1156,28 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Ralph Toastmasters Club</t>
+          <t>LSEG Sri Lanka Toastmasters</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Marketers Toastmasters Club</t>
+          <t>Ralph Toastmasters Club</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1195,19 +1195,19 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="8" t="n">
         <v>2</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -1216,28 +1216,28 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Torrington Toastmasters Club</t>
+          <t>IRD Toastmasters Club</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1246,28 +1246,28 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>IESL Ruhuna Toastmasters Club</t>
+          <t>Moratuwa Toastmasters</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E16" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1276,28 +1276,28 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>University of Moratuwa Toastmasters Club</t>
+          <t>Startup Colombo Toastmasters Club</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>IRD Toastmasters Club</t>
+          <t>Catalyst Toastmasters Club</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -1315,19 +1315,19 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>LSEG Sri Lanka Toastmasters</t>
+          <t>HSBC Global Service Centre</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -1345,19 +1345,19 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Sysco Labs SL Toastmasters</t>
+          <t>Marketers Toastmasters Club</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -1375,19 +1375,19 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Catalyst Toastmasters Club</t>
+          <t>SLT Toastmasters</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
@@ -1411,13 +1411,13 @@
         <v>0</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Sri Lanka Institute of Marketing Toastmasters Club</t>
+          <t>Sysco Labs SL Toastmasters</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -1441,13 +1441,13 @@
         <v>0</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G22" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1456,16 +1456,16 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>University of Colombo Toastmasters Club</t>
+          <t>University of Moratuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>0</v>
@@ -1474,39 +1474,9 @@
         <v>0</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>SLT Toastmasters</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1521,10 +1491,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -1547,7 +1517,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:24  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1592,82 +1562,10 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Startup Colombo Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>D-04</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Ralph Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>D-01</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D9" s="6" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>HSBC Global Service Centre</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>D-02</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Moratuwa Toastmasters</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>D-03</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1681,10 +1579,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -1707,7 +1605,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:24  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1743,74 +1641,12 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>CECB Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>D-04</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>IESL Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>D-04</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Torrington Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>D-02</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Marketers Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>D-01</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>2</v>
-      </c>
+          <t>No clubs yet</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/exports/division/Division_D.xlsx
+++ b/docs/exports/division/Division_D.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:31  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
         <v>19</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>7</v>
@@ -567,7 +567,7 @@
         <v>18</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -608,7 +608,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:31  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>4</v>
@@ -711,7 +711,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:31  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
         <v>11</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>3</v>
@@ -786,7 +786,7 @@
         <v>11</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>5</v>
@@ -798,23 +798,23 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Area 02</t>
+          <t>Area 01</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>4</v>
@@ -826,23 +826,23 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Area 01</t>
+          <t>Area 02</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>4</v>
@@ -861,7 +861,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="8" t="n">
         <v>0</v>
@@ -870,7 +870,7 @@
         <v>3</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H10" s="8" t="n">
         <v>4</v>
@@ -917,7 +917,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:31  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
         <v>8</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>3</v>
@@ -997,7 +997,7 @@
         <v>9</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -1018,7 +1018,7 @@
         <v>2</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>2</v>
@@ -1027,7 +1027,7 @@
         <v>2</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -1036,28 +1036,28 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CECB Toastmasters Club</t>
+          <t>IESL Toastmasters Club</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -1066,28 +1066,28 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>IESL Toastmasters Club</t>
+          <t>CECB Toastmasters Club</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1156,25 +1156,25 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>LSEG Sri Lanka Toastmasters</t>
+          <t>IRD Toastmasters Club</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="6" t="n">
         <v>2</v>
@@ -1186,22 +1186,22 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Ralph Toastmasters Club</t>
+          <t>LSEG Sri Lanka Toastmasters</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="8" t="n">
         <v>1</v>
@@ -1216,28 +1216,28 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>IRD Toastmasters Club</t>
+          <t>Moratuwa Toastmasters</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1246,16 +1246,16 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Moratuwa Toastmasters</t>
+          <t>Ralph Toastmasters Club</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="8" t="n">
         <v>0</v>
@@ -1267,7 +1267,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1517,7 +1517,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:31  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:31  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/division/Division_D.xlsx
+++ b/docs/exports/division/Division_D.xlsx
@@ -488,11 +488,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:31  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 2 / OMM</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -568,6 +568,13 @@
       </c>
       <c r="E7" s="6" t="n">
         <v>59</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Level 2 / OMM: from 2026-27, Toastmasters counts Online Meeting Mastery exploration completions toward the same DCP goals as Level 2 and reports them as one number, so the two can't be shown separately.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -585,7 +592,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -608,7 +615,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:31  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -627,7 +634,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Level 2 Rank</t>
+          <t>Level 2 / OMM Rank</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -687,7 +694,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -711,7 +718,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:31  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -740,7 +747,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 2 / OMM</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -894,7 +901,7 @@
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -917,7 +924,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:31  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -951,7 +958,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 2 / OMM</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -1517,7 +1524,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:31  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1612,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:31  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/division/Division_D.xlsx
+++ b/docs/exports/division/Division_D.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
